--- a/templates/tpl_booking_mssnhsk4hn77.xlsx
+++ b/templates/tpl_booking_mssnhsk4hn77.xlsx
@@ -414,276 +414,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:P69"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="495" customWidth="1" min="1" max="1"/>
-    <col width="322.2857142857143" customWidth="1" min="2" max="2"/>
-    <col width="335.5714285714286" customWidth="1" min="3" max="3"/>
-    <col width="219.4285714285714" customWidth="1" min="4" max="4"/>
-    <col width="92.71428571428571" customWidth="1" min="5" max="5"/>
-    <col width="92.71428571428571" customWidth="1" min="6" max="6"/>
-    <col width="92.71428571428571" customWidth="1" min="7" max="7"/>
-    <col width="202.4285714285714" customWidth="1" min="8" max="8"/>
-    <col width="302.2857142857143" customWidth="1" min="9" max="9"/>
-    <col width="229.1428571428571" customWidth="1" min="10" max="10"/>
-    <col width="146.2857142857143" customWidth="1" min="11" max="11"/>
-    <col width="99.42857142857143" customWidth="1" min="12" max="12"/>
-    <col width="99.42857142857143" customWidth="1" min="13" max="13"/>
-    <col width="99.42857142857143" customWidth="1" min="14" max="14"/>
-    <col width="239" customWidth="1" min="15" max="15"/>
-    <col width="735.4285714285714" customWidth="1" min="16" max="16"/>
-    <col width="335.5714285714286" customWidth="1" min="17" max="17"/>
-    <col width="335.5714285714286" customWidth="1" min="18" max="18"/>
-    <col width="335.5714285714286" customWidth="1" min="19" max="19"/>
-    <col width="335.5714285714286" customWidth="1" min="20" max="20"/>
-    <col width="335.5714285714286" customWidth="1" min="21" max="21"/>
-    <col width="335.5714285714286" customWidth="1" min="22" max="22"/>
-    <col width="335.5714285714286" customWidth="1" min="23" max="23"/>
-    <col width="335.5714285714286" customWidth="1" min="24" max="24"/>
-    <col width="335.5714285714286" customWidth="1" min="25" max="25"/>
-    <col width="335.5714285714286" customWidth="1" min="26" max="26"/>
-    <col width="335.5714285714286" customWidth="1" min="27" max="27"/>
-    <col width="335.5714285714286" customWidth="1" min="28" max="28"/>
-    <col width="335.5714285714286" customWidth="1" min="29" max="29"/>
-    <col width="335.5714285714286" customWidth="1" min="30" max="30"/>
-    <col width="335.5714285714286" customWidth="1" min="31" max="31"/>
-    <col width="335.5714285714286" customWidth="1" min="32" max="32"/>
-    <col width="335.5714285714286" customWidth="1" min="33" max="33"/>
-    <col width="335.5714285714286" customWidth="1" min="34" max="34"/>
-    <col width="335.5714285714286" customWidth="1" min="35" max="35"/>
-    <col width="335.5714285714286" customWidth="1" min="36" max="36"/>
-    <col width="335.5714285714286" customWidth="1" min="37" max="37"/>
-    <col width="335.5714285714286" customWidth="1" min="38" max="38"/>
-    <col width="335.5714285714286" customWidth="1" min="39" max="39"/>
-    <col width="335.5714285714286" customWidth="1" min="40" max="40"/>
-    <col width="335.5714285714286" customWidth="1" min="41" max="41"/>
-    <col width="335.5714285714286" customWidth="1" min="42" max="42"/>
-    <col width="335.5714285714286" customWidth="1" min="43" max="43"/>
-    <col width="335.5714285714286" customWidth="1" min="44" max="44"/>
-    <col width="335.5714285714286" customWidth="1" min="45" max="45"/>
-    <col width="335.5714285714286" customWidth="1" min="46" max="46"/>
-    <col width="335.5714285714286" customWidth="1" min="47" max="47"/>
-    <col width="335.5714285714286" customWidth="1" min="48" max="48"/>
-    <col width="335.5714285714286" customWidth="1" min="49" max="49"/>
-    <col width="335.5714285714286" customWidth="1" min="50" max="50"/>
-    <col width="335.5714285714286" customWidth="1" min="51" max="51"/>
-    <col width="335.5714285714286" customWidth="1" min="52" max="52"/>
-    <col width="335.5714285714286" customWidth="1" min="53" max="53"/>
-    <col width="335.5714285714286" customWidth="1" min="54" max="54"/>
-    <col width="335.5714285714286" customWidth="1" min="55" max="55"/>
-    <col width="335.5714285714286" customWidth="1" min="56" max="56"/>
-    <col width="335.5714285714286" customWidth="1" min="57" max="57"/>
-    <col width="335.5714285714286" customWidth="1" min="58" max="58"/>
-    <col width="335.5714285714286" customWidth="1" min="59" max="59"/>
-    <col width="335.5714285714286" customWidth="1" min="60" max="60"/>
-    <col width="335.5714285714286" customWidth="1" min="61" max="61"/>
-    <col width="335.5714285714286" customWidth="1" min="62" max="62"/>
-    <col width="335.5714285714286" customWidth="1" min="63" max="63"/>
-    <col width="335.5714285714286" customWidth="1" min="64" max="64"/>
-    <col width="335.5714285714286" customWidth="1" min="65" max="65"/>
-    <col width="335.5714285714286" customWidth="1" min="66" max="66"/>
-    <col width="335.5714285714286" customWidth="1" min="67" max="67"/>
-    <col width="335.5714285714286" customWidth="1" min="68" max="68"/>
-    <col width="335.5714285714286" customWidth="1" min="69" max="69"/>
-    <col width="335.5714285714286" customWidth="1" min="70" max="70"/>
-    <col width="335.5714285714286" customWidth="1" min="71" max="71"/>
-    <col width="335.5714285714286" customWidth="1" min="72" max="72"/>
-    <col width="335.5714285714286" customWidth="1" min="73" max="73"/>
-    <col width="335.5714285714286" customWidth="1" min="74" max="74"/>
-    <col width="335.5714285714286" customWidth="1" min="75" max="75"/>
-    <col width="335.5714285714286" customWidth="1" min="76" max="76"/>
-    <col width="335.5714285714286" customWidth="1" min="77" max="77"/>
-    <col width="335.5714285714286" customWidth="1" min="78" max="78"/>
-    <col width="335.5714285714286" customWidth="1" min="79" max="79"/>
-    <col width="335.5714285714286" customWidth="1" min="80" max="80"/>
-    <col width="335.5714285714286" customWidth="1" min="81" max="81"/>
-    <col width="335.5714285714286" customWidth="1" min="82" max="82"/>
-    <col width="335.5714285714286" customWidth="1" min="83" max="83"/>
-    <col width="335.5714285714286" customWidth="1" min="84" max="84"/>
-    <col width="335.5714285714286" customWidth="1" min="85" max="85"/>
-    <col width="335.5714285714286" customWidth="1" min="86" max="86"/>
-    <col width="335.5714285714286" customWidth="1" min="87" max="87"/>
-    <col width="335.5714285714286" customWidth="1" min="88" max="88"/>
-    <col width="335.5714285714286" customWidth="1" min="89" max="89"/>
-    <col width="335.5714285714286" customWidth="1" min="90" max="90"/>
-    <col width="335.5714285714286" customWidth="1" min="91" max="91"/>
-    <col width="335.5714285714286" customWidth="1" min="92" max="92"/>
-    <col width="335.5714285714286" customWidth="1" min="93" max="93"/>
-    <col width="335.5714285714286" customWidth="1" min="94" max="94"/>
-    <col width="335.5714285714286" customWidth="1" min="95" max="95"/>
-    <col width="335.5714285714286" customWidth="1" min="96" max="96"/>
-    <col width="335.5714285714286" customWidth="1" min="97" max="97"/>
-    <col width="335.5714285714286" customWidth="1" min="98" max="98"/>
-    <col width="335.5714285714286" customWidth="1" min="99" max="99"/>
-    <col width="335.5714285714286" customWidth="1" min="100" max="100"/>
-    <col width="335.5714285714286" customWidth="1" min="101" max="101"/>
-    <col width="335.5714285714286" customWidth="1" min="102" max="102"/>
-    <col width="335.5714285714286" customWidth="1" min="103" max="103"/>
-    <col width="335.5714285714286" customWidth="1" min="104" max="104"/>
-    <col width="335.5714285714286" customWidth="1" min="105" max="105"/>
-    <col width="335.5714285714286" customWidth="1" min="106" max="106"/>
-    <col width="335.5714285714286" customWidth="1" min="107" max="107"/>
-    <col width="335.5714285714286" customWidth="1" min="108" max="108"/>
-    <col width="335.5714285714286" customWidth="1" min="109" max="109"/>
-    <col width="335.5714285714286" customWidth="1" min="110" max="110"/>
-    <col width="335.5714285714286" customWidth="1" min="111" max="111"/>
-    <col width="335.5714285714286" customWidth="1" min="112" max="112"/>
-    <col width="335.5714285714286" customWidth="1" min="113" max="113"/>
-    <col width="335.5714285714286" customWidth="1" min="114" max="114"/>
-    <col width="335.5714285714286" customWidth="1" min="115" max="115"/>
-    <col width="335.5714285714286" customWidth="1" min="116" max="116"/>
-    <col width="335.5714285714286" customWidth="1" min="117" max="117"/>
-    <col width="335.5714285714286" customWidth="1" min="118" max="118"/>
-    <col width="335.5714285714286" customWidth="1" min="119" max="119"/>
-    <col width="335.5714285714286" customWidth="1" min="120" max="120"/>
-    <col width="335.5714285714286" customWidth="1" min="121" max="121"/>
-    <col width="335.5714285714286" customWidth="1" min="122" max="122"/>
-    <col width="335.5714285714286" customWidth="1" min="123" max="123"/>
-    <col width="335.5714285714286" customWidth="1" min="124" max="124"/>
-    <col width="335.5714285714286" customWidth="1" min="125" max="125"/>
-    <col width="335.5714285714286" customWidth="1" min="126" max="126"/>
-    <col width="335.5714285714286" customWidth="1" min="127" max="127"/>
-    <col width="335.5714285714286" customWidth="1" min="128" max="128"/>
-    <col width="335.5714285714286" customWidth="1" min="129" max="129"/>
-    <col width="335.5714285714286" customWidth="1" min="130" max="130"/>
-    <col width="335.5714285714286" customWidth="1" min="131" max="131"/>
-    <col width="335.5714285714286" customWidth="1" min="132" max="132"/>
-    <col width="335.5714285714286" customWidth="1" min="133" max="133"/>
-    <col width="335.5714285714286" customWidth="1" min="134" max="134"/>
-    <col width="335.5714285714286" customWidth="1" min="135" max="135"/>
-    <col width="335.5714285714286" customWidth="1" min="136" max="136"/>
-    <col width="335.5714285714286" customWidth="1" min="137" max="137"/>
-    <col width="335.5714285714286" customWidth="1" min="138" max="138"/>
-    <col width="335.5714285714286" customWidth="1" min="139" max="139"/>
-    <col width="335.5714285714286" customWidth="1" min="140" max="140"/>
-    <col width="335.5714285714286" customWidth="1" min="141" max="141"/>
-    <col width="335.5714285714286" customWidth="1" min="142" max="142"/>
-    <col width="335.5714285714286" customWidth="1" min="143" max="143"/>
-    <col width="335.5714285714286" customWidth="1" min="144" max="144"/>
-    <col width="335.5714285714286" customWidth="1" min="145" max="145"/>
-    <col width="335.5714285714286" customWidth="1" min="146" max="146"/>
-    <col width="335.5714285714286" customWidth="1" min="147" max="147"/>
-    <col width="335.5714285714286" customWidth="1" min="148" max="148"/>
-    <col width="335.5714285714286" customWidth="1" min="149" max="149"/>
-    <col width="335.5714285714286" customWidth="1" min="150" max="150"/>
-    <col width="335.5714285714286" customWidth="1" min="151" max="151"/>
-    <col width="335.5714285714286" customWidth="1" min="152" max="152"/>
-    <col width="335.5714285714286" customWidth="1" min="153" max="153"/>
-    <col width="335.5714285714286" customWidth="1" min="154" max="154"/>
-    <col width="335.5714285714286" customWidth="1" min="155" max="155"/>
-    <col width="335.5714285714286" customWidth="1" min="156" max="156"/>
-    <col width="335.5714285714286" customWidth="1" min="157" max="157"/>
-    <col width="335.5714285714286" customWidth="1" min="158" max="158"/>
-    <col width="335.5714285714286" customWidth="1" min="159" max="159"/>
-    <col width="335.5714285714286" customWidth="1" min="160" max="160"/>
-    <col width="335.5714285714286" customWidth="1" min="161" max="161"/>
-    <col width="335.5714285714286" customWidth="1" min="162" max="162"/>
-    <col width="335.5714285714286" customWidth="1" min="163" max="163"/>
-    <col width="335.5714285714286" customWidth="1" min="164" max="164"/>
-    <col width="335.5714285714286" customWidth="1" min="165" max="165"/>
-    <col width="335.5714285714286" customWidth="1" min="166" max="166"/>
-    <col width="335.5714285714286" customWidth="1" min="167" max="167"/>
-    <col width="335.5714285714286" customWidth="1" min="168" max="168"/>
-    <col width="335.5714285714286" customWidth="1" min="169" max="169"/>
-    <col width="335.5714285714286" customWidth="1" min="170" max="170"/>
-    <col width="335.5714285714286" customWidth="1" min="171" max="171"/>
-    <col width="335.5714285714286" customWidth="1" min="172" max="172"/>
-    <col width="335.5714285714286" customWidth="1" min="173" max="173"/>
-    <col width="335.5714285714286" customWidth="1" min="174" max="174"/>
-    <col width="335.5714285714286" customWidth="1" min="175" max="175"/>
-    <col width="335.5714285714286" customWidth="1" min="176" max="176"/>
-    <col width="335.5714285714286" customWidth="1" min="177" max="177"/>
-    <col width="335.5714285714286" customWidth="1" min="178" max="178"/>
-    <col width="335.5714285714286" customWidth="1" min="179" max="179"/>
-    <col width="335.5714285714286" customWidth="1" min="180" max="180"/>
-    <col width="335.5714285714286" customWidth="1" min="181" max="181"/>
-    <col width="335.5714285714286" customWidth="1" min="182" max="182"/>
-    <col width="335.5714285714286" customWidth="1" min="183" max="183"/>
-    <col width="335.5714285714286" customWidth="1" min="184" max="184"/>
-    <col width="335.5714285714286" customWidth="1" min="185" max="185"/>
-    <col width="335.5714285714286" customWidth="1" min="186" max="186"/>
-    <col width="335.5714285714286" customWidth="1" min="187" max="187"/>
-    <col width="335.5714285714286" customWidth="1" min="188" max="188"/>
-    <col width="335.5714285714286" customWidth="1" min="189" max="189"/>
-    <col width="335.5714285714286" customWidth="1" min="190" max="190"/>
-    <col width="335.5714285714286" customWidth="1" min="191" max="191"/>
-    <col width="335.5714285714286" customWidth="1" min="192" max="192"/>
-    <col width="335.5714285714286" customWidth="1" min="193" max="193"/>
-    <col width="335.5714285714286" customWidth="1" min="194" max="194"/>
-    <col width="335.5714285714286" customWidth="1" min="195" max="195"/>
-    <col width="335.5714285714286" customWidth="1" min="196" max="196"/>
-    <col width="335.5714285714286" customWidth="1" min="197" max="197"/>
-    <col width="335.5714285714286" customWidth="1" min="198" max="198"/>
-    <col width="335.5714285714286" customWidth="1" min="199" max="199"/>
-    <col width="335.5714285714286" customWidth="1" min="200" max="200"/>
-    <col width="335.5714285714286" customWidth="1" min="201" max="201"/>
-    <col width="335.5714285714286" customWidth="1" min="202" max="202"/>
-    <col width="335.5714285714286" customWidth="1" min="203" max="203"/>
-    <col width="335.5714285714286" customWidth="1" min="204" max="204"/>
-    <col width="335.5714285714286" customWidth="1" min="205" max="205"/>
-    <col width="335.5714285714286" customWidth="1" min="206" max="206"/>
-    <col width="335.5714285714286" customWidth="1" min="207" max="207"/>
-    <col width="335.5714285714286" customWidth="1" min="208" max="208"/>
-    <col width="335.5714285714286" customWidth="1" min="209" max="209"/>
-    <col width="335.5714285714286" customWidth="1" min="210" max="210"/>
-    <col width="335.5714285714286" customWidth="1" min="211" max="211"/>
-    <col width="335.5714285714286" customWidth="1" min="212" max="212"/>
-    <col width="335.5714285714286" customWidth="1" min="213" max="213"/>
-    <col width="335.5714285714286" customWidth="1" min="214" max="214"/>
-    <col width="335.5714285714286" customWidth="1" min="215" max="215"/>
-    <col width="335.5714285714286" customWidth="1" min="216" max="216"/>
-    <col width="335.5714285714286" customWidth="1" min="217" max="217"/>
-    <col width="335.5714285714286" customWidth="1" min="218" max="218"/>
-    <col width="335.5714285714286" customWidth="1" min="219" max="219"/>
-    <col width="335.5714285714286" customWidth="1" min="220" max="220"/>
-    <col width="335.5714285714286" customWidth="1" min="221" max="221"/>
-    <col width="335.5714285714286" customWidth="1" min="222" max="222"/>
-    <col width="335.5714285714286" customWidth="1" min="223" max="223"/>
-    <col width="335.5714285714286" customWidth="1" min="224" max="224"/>
-    <col width="335.5714285714286" customWidth="1" min="225" max="225"/>
-    <col width="335.5714285714286" customWidth="1" min="226" max="226"/>
-    <col width="335.5714285714286" customWidth="1" min="227" max="227"/>
-    <col width="335.5714285714286" customWidth="1" min="228" max="228"/>
-    <col width="335.5714285714286" customWidth="1" min="229" max="229"/>
-    <col width="335.5714285714286" customWidth="1" min="230" max="230"/>
-    <col width="335.5714285714286" customWidth="1" min="231" max="231"/>
-    <col width="335.5714285714286" customWidth="1" min="232" max="232"/>
-    <col width="335.5714285714286" customWidth="1" min="233" max="233"/>
-    <col width="335.5714285714286" customWidth="1" min="234" max="234"/>
-    <col width="335.5714285714286" customWidth="1" min="235" max="235"/>
-    <col width="335.5714285714286" customWidth="1" min="236" max="236"/>
-    <col width="335.5714285714286" customWidth="1" min="237" max="237"/>
-    <col width="335.5714285714286" customWidth="1" min="238" max="238"/>
-    <col width="335.5714285714286" customWidth="1" min="239" max="239"/>
-    <col width="335.5714285714286" customWidth="1" min="240" max="240"/>
-    <col width="335.5714285714286" customWidth="1" min="241" max="241"/>
-    <col width="335.5714285714286" customWidth="1" min="242" max="242"/>
-    <col width="335.5714285714286" customWidth="1" min="243" max="243"/>
-    <col width="335.5714285714286" customWidth="1" min="244" max="244"/>
-    <col width="335.5714285714286" customWidth="1" min="245" max="245"/>
-    <col width="335.5714285714286" customWidth="1" min="246" max="246"/>
-    <col width="335.5714285714286" customWidth="1" min="247" max="247"/>
-    <col width="335.5714285714286" customWidth="1" min="248" max="248"/>
-    <col width="335.5714285714286" customWidth="1" min="249" max="249"/>
-    <col width="335.5714285714286" customWidth="1" min="250" max="250"/>
-    <col width="335.5714285714286" customWidth="1" min="251" max="251"/>
-    <col width="335.5714285714286" customWidth="1" min="252" max="252"/>
-    <col width="335.5714285714286" customWidth="1" min="253" max="253"/>
-    <col width="335.5714285714286" customWidth="1" min="254" max="254"/>
-    <col width="335.5714285714286" customWidth="1" min="255" max="255"/>
-    <col width="335.5714285714286" customWidth="1" min="256" max="256"/>
-  </cols>
   <sheetData>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
+    <row r="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>ADD:广州市天河区林和西路157号保利中汇广场A1303房  CTC:SUSAN.QIN@DETRANS.CO TEL:020-38550807</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,79 +512,308 @@
           <t>航空运输委托书</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">       </t>
         </is>
       </c>
-    </row>
-    <row r="7"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>SHIPPER NAME &amp; ADDRESS（发货人公司名及地址）</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>ALSO NOTIFY（通知人）</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>same as Consignee</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>CONSIGNEE NAME &amp; ADDRESS （收货人公司名、地址及联系方式）</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>SPECIAL HANDLING INSTRUCTION</t>
         </is>
       </c>
-    </row>
-    <row r="15"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
     <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>带电件数：</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">       Without Battery</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">       Lithium ION batteries in compliance with Section II of PI </t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">       Lithium METAL batteries in compliance with Section II of PI </t>
         </is>
       </c>
-    </row>
-    <row r="20"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">带电货物需知:
@@ -771,25 +821,74 @@
 </t>
         </is>
       </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>Airport of Departure（始发站）</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Airport of Destination（到达站）</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve"> NAME OF CARRIER（航班 ）</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>AIR FREIGHT  (运费)</t>
@@ -802,11 +901,24 @@
           <t>GUANGZHOU</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>dubai</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,34 +926,74 @@
           <t>PACKAGES（件数）</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>GROSS WEIGHT （毛重）</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>VOLUME WEIGHT（体积）</t>
         </is>
       </c>
-    </row>
-    <row r="27"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>44ctns/8plts</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>645.4</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>10.56</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -849,23 +1001,131 @@
           <t>DIMENSIONS （尺寸）</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>NATURE OF GOODS （品名）</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>MARKS &amp; NUMBERS（唛头）</t>
         </is>
       </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -877,25 +1137,82 @@
           <t>（货物入仓时间）</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>PICKUP / SELF-DELIVERY（需提货/自入仓）</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>PICKUP ADDRESS (if different from shipper) （若需提货，请提供地址）</t>
         </is>
       </c>
-    </row>
-    <row r="37"/>
-    <row r="38"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
           <t>IF CARGO UNDER SELF-DELIVERY, PLEASE PROVIDE TRUCKER CONTACT DETAILS  （自入仓，请提供司机资料）</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -903,16 +1220,28 @@
           <t>TRUCKER NAME :</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">VEHICLE NUMBER : </t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUCKER PHONE NUMBER : </t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -920,19 +1249,62 @@
           <t>PLEASE PUT “TICK” AS APPROPRIATE (Please instruct clearly for PREPAID or COLLECT, otherwise, all charges will be debt to shipper or supplier, thanks)</t>
         </is>
       </c>
-    </row>
-    <row r="42"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>CHARGE ITEMS</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>DOCUMENTS TO BE ACCOMPANIED WITH AIRWAY BILL</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -940,6 +1312,7 @@
           <t>CHARGE DESCRIPTION</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>PREPAID</t>
@@ -950,11 +1323,13 @@
           <t>COLLECT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>)</t>
@@ -965,11 +1340,14 @@
           <t>Commercial Invoice</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>)</t>
@@ -987,11 +1365,16 @@
           <t>AIR FREIGHT CHARGE</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>)</t>
@@ -1002,11 +1385,14 @@
           <t>Customs Invoice</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>)</t>
@@ -1019,11 +1405,17 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>)</t>
@@ -1034,11 +1426,14 @@
           <t>Proforma Invoice</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>)</t>
@@ -1056,11 +1451,16 @@
           <t>SZX LOCAL CHARGES</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>)</t>
@@ -1071,11 +1471,14 @@
           <t>Packing List</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>)</t>
@@ -1088,11 +1491,17 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>)</t>
@@ -1103,11 +1512,14 @@
           <t>Declaration</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>)</t>
@@ -1120,11 +1532,17 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>)</t>
@@ -1135,11 +1553,14 @@
           <t>Quota Statement</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>)</t>
@@ -1152,11 +1573,17 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>)</t>
@@ -1167,6 +1594,12 @@
           <t>Others</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1174,24 +1607,66 @@
           <t>SHIPPER’S SIGNATURE &amp; CHOP（委托人签字盖章）</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">CONTACT PERSON </t>
         </is>
       </c>
-    </row>
-    <row r="52"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>DATE :2026/7/14</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>KIKI</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1199,6 +1674,20 @@
           <t xml:space="preserve">客户聲明： </t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1211,6 +1700,19 @@
           <t xml:space="preserve">托運的空運貨物由可靠的人員在不受干擾的處所處理。 </t>
         </is>
       </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1223,6 +1725,19 @@
           <t xml:space="preserve">在本公司準備、儲存和運送托運的空運貨物期間，這些貨物均獲妥善保護，不受干擾。 </t>
         </is>
       </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1235,6 +1750,19 @@
           <t>本人同意，任何托運的空運貨物的包裝和內含物品可基於保安理由而接受檢查。</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1247,6 +1775,19 @@
           <t>托運的空運貨物並無藏有任何爆炸品或燃燒裝置。</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1259,6 +1800,19 @@
           <t>本人同意接受民航處或其代理人突擊巡查或在預先通知後巡查。本人亦同意直接向民航處提供任何文件，</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1266,6 +1820,20 @@
           <t xml:space="preserve">以便監察本公司有否遵從《托運人規定文件》和《管制代理人制度空運貨物處理程序》訂明的保安規定，以及民航處不時發出的任何其他指示。 </t>
         </is>
       </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1278,6 +1846,19 @@
           <t xml:space="preserve">本人會確保本公司持續遵從《托運人規定文件》訂明的保安規定，並把這些規定告知可接觸空運貨物及／或相關裝運單據的所有人員。 </t>
         </is>
       </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1290,6 +1871,19 @@
           <t xml:space="preserve">在下列情況下，本人會在合理時間內盡快向認可本公司為已知托運人的管制代理人提供有關詳情： </t>
         </is>
       </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1302,6 +1896,19 @@
           <t xml:space="preserve">更換負責實施及監管貨物保安措施的主管人； </t>
         </is>
       </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1314,6 +1921,19 @@
           <t xml:space="preserve">更改處所或可能影響保安的程序； </t>
         </is>
       </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1326,6 +1946,19 @@
           <t xml:space="preserve">本公司停業，不再處理空運貨物；或 </t>
         </is>
       </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1338,6 +1971,19 @@
           <t xml:space="preserve">本公司不再實施《托運人規定文件》所訂明的保安措施。  </t>
         </is>
       </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1345,81 +1991,22 @@
           <t xml:space="preserve">本公司明白故意作出虛假聲明可能遭檢控，本公司並同意為此聲明承擔責任。   </t>
         </is>
       </c>
-    </row>
-    <row r="69"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="I25:N25"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A26:B27"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="C30:J30"/>
-    <mergeCell ref="A9:H13"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="I15:P15"/>
-    <mergeCell ref="I9:P13"/>
-    <mergeCell ref="I28:N28"/>
-    <mergeCell ref="O25:P28"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="L53:P53"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="A41:P42"/>
-    <mergeCell ref="A47:B48"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="K37:P38"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="A15:H23"/>
-    <mergeCell ref="A39:P39"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="D36:J36"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C26:H27"/>
-    <mergeCell ref="I26:N27"/>
-    <mergeCell ref="I21:P23"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="C31:J35"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="I14:P14"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="K34:P34"/>
-    <mergeCell ref="D49:E50"/>
-    <mergeCell ref="I8:P8"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="F43:P43"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="L52:P52"/>
-    <mergeCell ref="A45:B46"/>
-    <mergeCell ref="D47:E48"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="B53:K53"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="D45:E46"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="K35:P35"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="K29:P29"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1430,10 +2017,502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="M33:M33"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
     <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>0.576</v>
       </c>
